--- a/corrected-bank-specimens-for-user/05-absa/parsed-excel/ABSA cocoa purchases call deposit(2086268)-september,2023 - parsed.xlsx
+++ b/corrected-bank-specimens-for-user/05-absa/parsed-excel/ABSA cocoa purchases call deposit(2086268)-september,2023 - parsed.xlsx
@@ -429,7 +429,7 @@
         <v>Exported</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-07-08T16:17:01.086Z</v>
+        <v>2026-07-14T13:50:03.838Z</v>
       </c>
     </row>
     <row r="5">

--- a/corrected-bank-specimens-for-user/05-absa/parsed-excel/ABSA cocoa purchases call deposit(2086268)-september,2023 - parsed.xlsx
+++ b/corrected-bank-specimens-for-user/05-absa/parsed-excel/ABSA cocoa purchases call deposit(2086268)-september,2023 - parsed.xlsx
@@ -429,7 +429,7 @@
         <v>Exported</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-07-14T13:50:03.838Z</v>
+        <v>2026-07-17T19:29:57.666Z</v>
       </c>
     </row>
     <row r="5">
